--- a/Toronto_Raptors_2025-26_stats.xlsx
+++ b/Toronto_Raptors_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,6 +1164,60 @@
       </c>
       <c r="P13" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" t="n">
+        <v>14</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="n">
+        <v>22</v>
+      </c>
+      <c r="I14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>22</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>12</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1177,7 +1231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1907,6 +1961,60 @@
         <v>1</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1921,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2652,6 +2760,60 @@
       </c>
       <c r="P13" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2665,7 +2827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3395,6 +3557,60 @@
         <v>2</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3431,7 +3647,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.5</v>
+        <v>20.38461538461538</v>
       </c>
     </row>
     <row r="3">
@@ -3441,7 +3657,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.16666666666667</v>
+        <v>19.69230769230769</v>
       </c>
     </row>
     <row r="4">
@@ -3451,7 +3667,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.08333333333333</v>
+        <v>19.30769230769231</v>
       </c>
     </row>
     <row r="5">
@@ -3461,7 +3677,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.08333333333333</v>
+        <v>15.76923076923077</v>
       </c>
     </row>
     <row r="6">
@@ -3471,7 +3687,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.75</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="7">
@@ -3481,7 +3697,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.363636363636363</v>
+        <v>9.583333333333334</v>
       </c>
     </row>
     <row r="8">
@@ -3491,7 +3707,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.777777777777779</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="9">
@@ -3501,7 +3717,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.5</v>
+        <v>7.538461538461538</v>
       </c>
     </row>
     <row r="10">
@@ -3511,7 +3727,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.5</v>
+        <v>6.538461538461538</v>
       </c>
     </row>
     <row r="11">
@@ -3531,7 +3747,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.222222222222222</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="13">
@@ -3597,7 +3813,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.166666666666667</v>
+        <v>6.230769230769231</v>
       </c>
     </row>
     <row r="3">
@@ -3607,7 +3823,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.166666666666667</v>
+        <v>5.230769230769231</v>
       </c>
     </row>
     <row r="4">
@@ -3617,13 +3833,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.166666666666667</v>
+        <v>5.076923076923077</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3633,31 +3849,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3.846153846153846</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jakob Poeltl</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.875</v>
+        <v>1.916666666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Jakob Poeltl</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.818181818181818</v>
+        <v>1.777777777777778</v>
       </c>
     </row>
     <row r="9">
@@ -3667,13 +3883,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.222222222222222</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ja'Kobe Walter</t>
+          <t>Ochai Agbaji</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -3683,11 +3899,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ochai Agbaji</t>
+          <t>Ja'Kobe Walter</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12">
@@ -3707,7 +3923,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="14">
@@ -3763,7 +3979,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.583333333333333</v>
+        <v>7.846153846153846</v>
       </c>
     </row>
     <row r="3">
@@ -3773,7 +3989,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.125</v>
+        <v>7.333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -3783,7 +3999,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.083333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -3793,7 +4009,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>5.076923076923077</v>
       </c>
     </row>
     <row r="6">
@@ -3803,7 +4019,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.416666666666667</v>
+        <v>4.307692307692307</v>
       </c>
     </row>
     <row r="7">
@@ -3813,7 +4029,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.888888888888889</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="8">
@@ -3823,27 +4039,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.545454545454545</v>
+        <v>3.583333333333333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ochai Agbaji</t>
+          <t>Gradey Dick</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.111111111111111</v>
+        <v>2.307692307692307</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gradey Dick</t>
+          <t>Ochai Agbaji</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>2.111111111111111</v>
       </c>
     </row>
     <row r="11">
@@ -3853,7 +4069,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.833333333333333</v>
+        <v>1.692307692307692</v>
       </c>
     </row>
     <row r="12">
@@ -3863,7 +4079,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.444444444444444</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13">
@@ -3929,77 +4145,77 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.333333333333333</v>
+        <v>2.307692307692307</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Scottie Barnes</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.75</v>
+        <v>1.846153846153846</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Scottie Barnes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.75</v>
+        <v>1.615384615384615</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gradey Dick</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.25</v>
+        <v>1.230769230769231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>Gradey Dick</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.25</v>
+        <v>1.153846153846154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Jamison Battle</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.166666666666667</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jamison Battle</t>
+          <t>Sandro Mamukelashvili</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.1</v>
+        <v>1.083333333333333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sandro Mamukelashvili</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.090909090909091</v>
+        <v>1.076923076923077</v>
       </c>
     </row>
     <row r="10">
@@ -4009,7 +4225,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11">
@@ -4019,7 +4235,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12">
@@ -4073,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4355,6 +4571,27 @@
         <v>239</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>129</v>
+      </c>
+      <c r="D14" t="n">
+        <v>111</v>
+      </c>
+      <c r="E14" t="n">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
